--- a/plans/kitchen-boq.xlsx
+++ b/plans/kitchen-boq.xlsx
@@ -515,7 +515,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bill of quantities · kitchen · Betalbatim pub</t>
+          <t>Bill of quantities · kitchen · Cabin East, Betalbatim</t>
         </is>
       </c>
     </row>
